--- a/EquiposUnidos/app/src/main/res/raw/template_user.xlsx
+++ b/EquiposUnidos/app/src/main/res/raw/template_user.xlsx
@@ -5,36 +5,32 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\Informacion plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C762F83E-C174-41F8-AF1E-2D6926FC908C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813BAB3C-383C-4536-815E-E56465BFF8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="897" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="897" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Control de Cambios " sheetId="16" r:id="rId1"/>
-    <sheet name="Eider Melendez" sheetId="10" r:id="rId2"/>
+    <sheet name="Eider Melendez" sheetId="10" r:id="rId1"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Eider Melendez'!$B$10:$M$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eider Melendez'!$B$10:$M$68</definedName>
     <definedName name="AÑO">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Control de Cambios '!$A$1:$G$15</definedName>
     <definedName name="Cargos">[1]Datos!$D$2:$D$39</definedName>
     <definedName name="CERT">#REF!</definedName>
     <definedName name="CREDITO">#REF!</definedName>
     <definedName name="DEPENDIENTE">#REF!</definedName>
-    <definedName name="DEPENDIENTE2" localSheetId="0">[2]Hoja1!$C$1:$C$65536</definedName>
     <definedName name="DEPENDIENTE2">[2]Hoja1!$C$1:$C$65536</definedName>
     <definedName name="DÍA">#REF!</definedName>
     <definedName name="EXPERIENCIA">#REF!</definedName>
     <definedName name="GARANTIA">#REF!</definedName>
     <definedName name="INDEPENDIENTE">#REF!</definedName>
-    <definedName name="INDEPENDIENTE2" localSheetId="0">[2]Hoja1!$B$1:$B$65536</definedName>
     <definedName name="INDEPENDIENTE2">[2]Hoja1!$B$1:$B$65536</definedName>
     <definedName name="INFO">#REF!</definedName>
     <definedName name="INICIO">#REF!</definedName>
@@ -52,27 +48,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="21">
   <si>
     <t>NOVEDADES DE NOMINA</t>
-  </si>
-  <si>
-    <t>Código del documento:</t>
   </si>
   <si>
     <t>FT-CONT-07</t>
   </si>
   <si>
-    <t>Versión No.</t>
-  </si>
-  <si>
     <t>Fecha</t>
-  </si>
-  <si>
-    <t>Descripción de la modificación</t>
-  </si>
-  <si>
-    <t>Responsable</t>
   </si>
   <si>
     <t>Código:</t>
@@ -123,35 +107,6 @@
     <t>Eider Melendez Gomez</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTROL DE CAMBIOS   </t>
-  </si>
-  <si>
-    <t>Control de Cambios de estructura y actualización de formato</t>
-  </si>
-  <si>
-    <t>El cambio corresponde a:
- Cambio por estructura del formato o
- Cambio por actualización del documento</t>
-  </si>
-  <si>
-    <t>Creación del documento</t>
-  </si>
-  <si>
-    <t>Cambio por estructura del formato</t>
-  </si>
-  <si>
-    <t>Coordinador HSEQ</t>
-  </si>
-  <si>
-    <t>Cambio por actualización del documento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se realiza cambio de logo, se modifica el tipo de letra, se cambia el color de las celdas, </t>
-  </si>
-  <si>
-    <t>Se realiza modificación en la estructura del control de cambio, se incluyen nuevas casillas con base a la automatización de proceso.</t>
-  </si>
-  <si>
     <t>Ingreso</t>
   </si>
   <si>
@@ -162,13 +117,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm:ss;@"/>
     <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
-    <numFmt numFmtId="167" formatCode="[$-C0A]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,33 +203,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Muller Regular"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Muller Regular"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="Muller Regular"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Muller Regular"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Muller Regular"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,24 +249,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -645,173 +562,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -870,159 +627,38 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="8" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1076,19 +712,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1117,61 +761,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304801</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1285876</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>30838</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46F63E40-0166-4394-9327-59E1FE6DF4AE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="561976" y="238126"/>
-          <a:ext cx="2171700" cy="783312"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2046,212 +1635,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE89CF09-F61E-43F1-829E-0A2AC5F591EF}">
-  <sheetPr>
-    <tabColor theme="1"/>
-  </sheetPr>
-  <dimension ref="A1:AD16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="3.88671875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="23" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="49.33203125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="48.109375" style="22" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="22" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="23" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="24" hidden="1" customWidth="1"/>
-    <col min="10" max="22" width="11.44140625" style="23" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="18.88671875" style="23" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="10.6640625" style="23" hidden="1" customWidth="1"/>
-    <col min="25" max="26" width="26" style="23" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.88671875" style="23" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" style="23" hidden="1" customWidth="1"/>
-    <col min="29" max="30" width="26" style="23" hidden="1" customWidth="1"/>
-    <col min="31" max="16384" width="11.44140625" style="23" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:9" ht="13.2">
-      <c r="B1" s="22"/>
-      <c r="D1" s="22"/>
-    </row>
-    <row r="2" spans="2:9" s="25" customFormat="1" ht="26.25" customHeight="1">
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="39"/>
-    </row>
-    <row r="3" spans="2:9" s="25" customFormat="1" ht="26.25" customHeight="1">
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="42"/>
-    </row>
-    <row r="4" spans="2:9" s="25" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="42"/>
-    </row>
-    <row r="5" spans="2:9" s="25" customFormat="1" ht="9" customHeight="1">
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="45"/>
-    </row>
-    <row r="6" spans="2:9" ht="12.75" customHeight="1"/>
-    <row r="7" spans="2:9" ht="14.25" customHeight="1"/>
-    <row r="8" spans="2:9" ht="23.25" customHeight="1">
-      <c r="B8" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-    </row>
-    <row r="9" spans="2:9" ht="23.25" customHeight="1">
-      <c r="B9" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="26"/>
-    </row>
-    <row r="10" spans="2:9" ht="13.2">
-      <c r="B10" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="28"/>
-    </row>
-    <row r="11" spans="2:9" ht="13.2">
-      <c r="B11" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="42" customHeight="1">
-      <c r="B12" s="50"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="46"/>
-    </row>
-    <row r="13" spans="2:9" ht="24" customHeight="1">
-      <c r="B13" s="29">
-        <v>1</v>
-      </c>
-      <c r="C13" s="30">
-        <v>43644</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="24" t="str">
-        <f>+D13</f>
-        <v>Creación del documento</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="28.5" customHeight="1">
-      <c r="B14" s="29">
-        <v>2</v>
-      </c>
-      <c r="C14" s="30">
-        <v>45211</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" ht="46.5" customHeight="1">
-      <c r="B15" s="31">
-        <v>3</v>
-      </c>
-      <c r="C15" s="32">
-        <v>45211</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="24" t="str">
-        <f t="shared" ref="I15" si="0">+D15</f>
-        <v>Se realiza modificación en la estructura del control de cambio, se incluyen nuevas casillas con base a la automatización de proceso.</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="12.75" customHeight="1"/>
-  </sheetData>
-  <sheetProtection formatRows="0" sort="0"/>
-  <mergeCells count="10">
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="B2:C5"/>
-    <mergeCell ref="D2:F5"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:C10"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E15" xr:uid="{E64D1D77-3136-4351-86ED-A58A5B9ED1C8}">
-      <formula1>"Cambio por estructura del formato, Cambio por actualización del documento"</formula1>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="La fecha mínima debe ser hoy" sqref="C13:C15" xr:uid="{9F17AB2E-A2C4-4BDF-9804-DF48309211A0}">
-      <formula1>36891</formula1>
-      <formula2>219512</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="55" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EA5052-75FA-4F7D-972E-2DFD2D6D72EA}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -2274,424 +1657,421 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="14.4">
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="77" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
       <c r="L2" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="1" t="str">
-        <f>+'Control de Cambios '!D10</f>
-        <v>FT-CONT-07</v>
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="14.4">
-      <c r="B3" s="71"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
       <c r="L3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="14.4">
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="17">
+        <v>45211</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="14.4">
+      <c r="B6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="2">
-        <f>MAX('Control de Cambios '!B13:B150)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" ht="14.4">
-      <c r="B4" s="74"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="20" t="s">
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="5"/>
+    </row>
+    <row r="7" spans="2:14" ht="14.4">
+      <c r="B7" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="53">
+        <v>1128048038</v>
+      </c>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="2:14" ht="14.4">
+      <c r="B8" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="17">
-        <f>MAX('Control de Cambios '!C13:C150)</f>
-        <v>45211</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="14.4">
-      <c r="B6" s="84" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="85" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="5"/>
-    </row>
-    <row r="7" spans="2:14" ht="14.4">
-      <c r="B7" s="84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="87">
-        <v>1128048038</v>
-      </c>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="5"/>
-    </row>
-    <row r="8" spans="2:14" ht="14.4">
-      <c r="B8" s="84" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="84"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="88"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="54"/>
       <c r="N8" s="21"/>
     </row>
     <row r="9" spans="2:14" ht="14.4">
-      <c r="B9" s="90"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="90"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="90"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="56"/>
     </row>
     <row r="10" spans="2:14" ht="14.4">
       <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="29"/>
+      <c r="F10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="91" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="7" t="s">
+      <c r="K10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" s="94"/>
+      <c r="M10" s="31"/>
     </row>
     <row r="11" spans="2:14" ht="14.4">
       <c r="B11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C11" s="32"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="12"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" spans="2:14" ht="14.4">
       <c r="B12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C12" s="33"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
       <c r="F12" s="4"/>
       <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="67"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
     </row>
     <row r="13" spans="2:14" ht="14.4">
       <c r="B13" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="61"/>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="95"/>
+      <c r="J13" s="22"/>
       <c r="K13" s="14"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
     </row>
     <row r="14" spans="2:14" ht="14.4">
       <c r="B14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C14" s="59"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="95"/>
+      <c r="J14" s="22"/>
       <c r="K14" s="14"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
     </row>
     <row r="15" spans="2:14" ht="14.4">
       <c r="B15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="12"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
     </row>
     <row r="16" spans="2:14" ht="14.4">
       <c r="B16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="4"/>
       <c r="G16" s="11"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
     </row>
     <row r="17" spans="2:30" ht="14.4">
       <c r="B17" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C17" s="58"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="61"/>
       <c r="F17" s="15"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="95"/>
+      <c r="J17" s="22"/>
       <c r="K17" s="14"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
     </row>
     <row r="18" spans="2:30" ht="14.4">
       <c r="B18" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C18" s="59"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="63"/>
       <c r="F18" s="14"/>
       <c r="G18" s="16"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="95"/>
+      <c r="J18" s="22"/>
       <c r="K18" s="14"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
     </row>
     <row r="19" spans="2:30" ht="14.4">
       <c r="B19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C19" s="32"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
       <c r="F19" s="12"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
     </row>
     <row r="20" spans="2:30" ht="15.75" customHeight="1">
       <c r="B20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C20" s="33"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="4"/>
       <c r="G20" s="11"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
     </row>
     <row r="21" spans="2:30" ht="15" customHeight="1">
       <c r="B21" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="61"/>
       <c r="F21" s="15"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
-      <c r="J21" s="95"/>
+      <c r="J21" s="22"/>
       <c r="K21" s="14"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
     </row>
     <row r="22" spans="2:30" ht="15" customHeight="1">
       <c r="B22" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C22" s="59"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="63"/>
       <c r="F22" s="14"/>
       <c r="G22" s="16"/>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
-      <c r="J22" s="95"/>
+      <c r="J22" s="22"/>
       <c r="K22" s="14"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
     </row>
     <row r="23" spans="2:30" ht="15" customHeight="1">
       <c r="B23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="12"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
     </row>
     <row r="24" spans="2:30" ht="15" customHeight="1">
       <c r="B24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="61"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="26"/>
       <c r="F24" s="4"/>
       <c r="G24" s="11"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
     </row>
     <row r="25" spans="2:30" ht="15" customHeight="1">
       <c r="B25" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C25" s="58"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="61"/>
       <c r="F25" s="15"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
-      <c r="J25" s="95"/>
+      <c r="J25" s="22"/>
       <c r="K25" s="14"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
     </row>
     <row r="26" spans="2:30" ht="15" customHeight="1">
       <c r="B26" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C26" s="59"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="63"/>
       <c r="F26" s="14"/>
       <c r="G26" s="16"/>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="95"/>
+      <c r="J26" s="22"/>
       <c r="K26" s="14"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -2712,19 +2092,19 @@
     </row>
     <row r="27" spans="2:30" ht="15" customHeight="1">
       <c r="B27" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="60"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C27" s="32"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -2745,35 +2125,35 @@
     </row>
     <row r="28" spans="2:30" ht="15" customHeight="1">
       <c r="B28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="61"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C28" s="33"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
     </row>
     <row r="29" spans="2:30" ht="15" customHeight="1">
       <c r="B29" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C29" s="58"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="61"/>
       <c r="F29" s="15"/>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
-      <c r="J29" s="95"/>
+      <c r="J29" s="22"/>
       <c r="K29" s="14"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -2794,67 +2174,67 @@
     </row>
     <row r="30" spans="2:30" ht="15" customHeight="1">
       <c r="B30" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C30" s="59"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="63"/>
       <c r="F30" s="14"/>
       <c r="G30" s="16"/>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
-      <c r="J30" s="95"/>
+      <c r="J30" s="22"/>
       <c r="K30" s="14"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
     </row>
     <row r="31" spans="2:30" ht="15" customHeight="1">
       <c r="B31" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C31" s="32"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="12"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
-      <c r="L31" s="66"/>
-      <c r="M31" s="66"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
     </row>
     <row r="32" spans="2:30" ht="15" customHeight="1">
       <c r="B32" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C32" s="33"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
       <c r="F32" s="4"/>
       <c r="G32" s="11"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
     </row>
     <row r="33" spans="2:30" ht="15" customHeight="1">
       <c r="B33" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C33" s="58"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="61"/>
       <c r="F33" s="15"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
-      <c r="J33" s="95"/>
+      <c r="J33" s="22"/>
       <c r="K33" s="14"/>
-      <c r="L33" s="59"/>
-      <c r="M33" s="59"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="65"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -2875,51 +2255,51 @@
     </row>
     <row r="34" spans="2:30" ht="15.75" customHeight="1">
       <c r="B34" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C34" s="59"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="63"/>
       <c r="F34" s="14"/>
       <c r="G34" s="16"/>
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
-      <c r="J34" s="95"/>
+      <c r="J34" s="22"/>
       <c r="K34" s="14"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="58"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="64"/>
     </row>
     <row r="35" spans="2:30" ht="15" customHeight="1">
       <c r="B35" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C35" s="32"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="12"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="66"/>
-      <c r="M35" s="66"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
     </row>
     <row r="36" spans="2:30" ht="15" customHeight="1">
       <c r="B36" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="61"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C36" s="33"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="4"/>
       <c r="G36" s="11"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
@@ -2940,67 +2320,67 @@
     </row>
     <row r="37" spans="2:30" ht="15" customHeight="1">
       <c r="B37" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C37" s="58"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="61"/>
       <c r="F37" s="15"/>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
-      <c r="J37" s="95"/>
+      <c r="J37" s="22"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="58"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="64"/>
     </row>
     <row r="38" spans="2:30" ht="15" customHeight="1">
       <c r="B38" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="53"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C38" s="59"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="63"/>
       <c r="F38" s="14"/>
       <c r="G38" s="16"/>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
-      <c r="J38" s="95"/>
+      <c r="J38" s="22"/>
       <c r="K38" s="14"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="58"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
     </row>
     <row r="39" spans="2:30" ht="15" customHeight="1">
       <c r="B39" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="60"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C39" s="32"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="24"/>
       <c r="F39" s="12"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="66"/>
-      <c r="M39" s="66"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
     </row>
     <row r="40" spans="2:30" ht="15" customHeight="1">
       <c r="B40" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="61"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C40" s="33"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="26"/>
       <c r="F40" s="4"/>
       <c r="G40" s="11"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="67"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -3021,515 +2401,515 @@
     </row>
     <row r="41" spans="2:30" ht="15.75" customHeight="1">
       <c r="B41" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="52"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C41" s="58"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
-      <c r="J41" s="95"/>
+      <c r="J41" s="22"/>
       <c r="K41" s="14"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
+      <c r="L41" s="64"/>
+      <c r="M41" s="64"/>
     </row>
     <row r="42" spans="2:30" ht="15.75" customHeight="1">
       <c r="B42" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="53"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C42" s="59"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="63"/>
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
-      <c r="J42" s="95"/>
+      <c r="J42" s="22"/>
       <c r="K42" s="14"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
     </row>
     <row r="43" spans="2:30" ht="15.75" customHeight="1">
       <c r="B43" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C43" s="32"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="24"/>
       <c r="F43" s="12"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="66"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="27"/>
     </row>
     <row r="44" spans="2:30" ht="15.75" customHeight="1">
       <c r="B44" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="61"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C44" s="33"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="4"/>
       <c r="G44" s="11"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
-      <c r="L44" s="67"/>
-      <c r="M44" s="67"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="57"/>
     </row>
     <row r="45" spans="2:30" ht="15.75" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="52"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C45" s="58"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="61"/>
       <c r="F45" s="15"/>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
-      <c r="J45" s="95"/>
+      <c r="J45" s="22"/>
       <c r="K45" s="14"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
+      <c r="L45" s="64"/>
+      <c r="M45" s="64"/>
     </row>
     <row r="46" spans="2:30" ht="15.75" customHeight="1">
       <c r="B46" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="53"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C46" s="59"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="63"/>
       <c r="F46" s="14"/>
       <c r="G46" s="16"/>
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
-      <c r="J46" s="95"/>
+      <c r="J46" s="22"/>
       <c r="K46" s="14"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="59"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
     </row>
     <row r="47" spans="2:30" ht="15.75" customHeight="1">
       <c r="B47" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C47" s="32"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="24"/>
       <c r="F47" s="12"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
-      <c r="L47" s="66"/>
-      <c r="M47" s="66"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27"/>
     </row>
     <row r="48" spans="2:30" ht="15.75" customHeight="1">
       <c r="B48" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" s="61"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C48" s="33"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="26"/>
       <c r="F48" s="4"/>
       <c r="G48" s="11"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
-      <c r="L48" s="67"/>
-      <c r="M48" s="67"/>
+      <c r="L48" s="57"/>
+      <c r="M48" s="57"/>
     </row>
     <row r="49" spans="2:13" ht="15.75" customHeight="1">
       <c r="B49" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C49" s="58"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="61"/>
       <c r="F49" s="15"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
-      <c r="J49" s="95"/>
+      <c r="J49" s="22"/>
       <c r="K49" s="14"/>
-      <c r="L49" s="58"/>
-      <c r="M49" s="58"/>
+      <c r="L49" s="64"/>
+      <c r="M49" s="64"/>
     </row>
     <row r="50" spans="2:13" ht="15.75" customHeight="1">
       <c r="B50" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="53"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C50" s="59"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="63"/>
       <c r="F50" s="14"/>
       <c r="G50" s="16"/>
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
-      <c r="J50" s="95"/>
+      <c r="J50" s="22"/>
       <c r="K50" s="14"/>
-      <c r="L50" s="59"/>
-      <c r="M50" s="59"/>
+      <c r="L50" s="65"/>
+      <c r="M50" s="65"/>
     </row>
     <row r="51" spans="2:13" ht="15.75" customHeight="1">
       <c r="B51" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="62"/>
-      <c r="E51" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C51" s="32"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="24"/>
       <c r="F51" s="12"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
-      <c r="L51" s="66"/>
-      <c r="M51" s="66"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="27"/>
     </row>
     <row r="52" spans="2:13" ht="15.75" customHeight="1">
       <c r="B52" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" s="61"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C52" s="33"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
       <c r="F52" s="4"/>
       <c r="G52" s="11"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
-      <c r="L52" s="67"/>
-      <c r="M52" s="67"/>
+      <c r="L52" s="57"/>
+      <c r="M52" s="57"/>
     </row>
     <row r="53" spans="2:13" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="52"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C53" s="58"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="61"/>
       <c r="F53" s="15"/>
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
-      <c r="J53" s="95"/>
+      <c r="J53" s="22"/>
       <c r="K53" s="14"/>
-      <c r="L53" s="58"/>
-      <c r="M53" s="58"/>
+      <c r="L53" s="64"/>
+      <c r="M53" s="64"/>
     </row>
     <row r="54" spans="2:13" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="53"/>
-      <c r="D54" s="56"/>
-      <c r="E54" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C54" s="59"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="63"/>
       <c r="F54" s="14"/>
       <c r="G54" s="16"/>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
-      <c r="J54" s="95"/>
+      <c r="J54" s="22"/>
       <c r="K54" s="14"/>
-      <c r="L54" s="59"/>
-      <c r="M54" s="59"/>
+      <c r="L54" s="65"/>
+      <c r="M54" s="65"/>
     </row>
     <row r="55" spans="2:13" ht="15.75" customHeight="1">
       <c r="B55" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="60"/>
-      <c r="D55" s="62"/>
-      <c r="E55" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C55" s="32"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="24"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
-      <c r="L55" s="66"/>
-      <c r="M55" s="66"/>
+      <c r="L55" s="27"/>
+      <c r="M55" s="27"/>
     </row>
     <row r="56" spans="2:13" ht="15.75" customHeight="1">
       <c r="B56" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C56" s="61"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C56" s="33"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="26"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
-      <c r="L56" s="67"/>
-      <c r="M56" s="67"/>
+      <c r="L56" s="57"/>
+      <c r="M56" s="57"/>
     </row>
     <row r="57" spans="2:13" ht="15.75" customHeight="1">
       <c r="B57" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" s="52"/>
-      <c r="D57" s="54"/>
-      <c r="E57" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C57" s="58"/>
+      <c r="D57" s="60"/>
+      <c r="E57" s="61"/>
       <c r="F57" s="15"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
-      <c r="J57" s="95"/>
+      <c r="J57" s="22"/>
       <c r="K57" s="14"/>
-      <c r="L57" s="58"/>
-      <c r="M57" s="58"/>
+      <c r="L57" s="64"/>
+      <c r="M57" s="64"/>
     </row>
     <row r="58" spans="2:13" ht="15.75" customHeight="1">
       <c r="B58" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="53"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C58" s="59"/>
+      <c r="D58" s="62"/>
+      <c r="E58" s="63"/>
       <c r="F58" s="14"/>
       <c r="G58" s="16"/>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
-      <c r="J58" s="95"/>
+      <c r="J58" s="22"/>
       <c r="K58" s="14"/>
-      <c r="L58" s="59"/>
-      <c r="M58" s="59"/>
+      <c r="L58" s="65"/>
+      <c r="M58" s="65"/>
     </row>
     <row r="59" spans="2:13" ht="15.75" customHeight="1">
       <c r="B59" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" s="60"/>
-      <c r="D59" s="62"/>
-      <c r="E59" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C59" s="32"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="24"/>
       <c r="F59" s="12"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
-      <c r="L59" s="66"/>
-      <c r="M59" s="66"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
     </row>
     <row r="60" spans="2:13" ht="15.75" customHeight="1">
       <c r="B60" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C60" s="61"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C60" s="33"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="26"/>
       <c r="F60" s="4"/>
       <c r="G60" s="11"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="67"/>
-      <c r="M60" s="67"/>
+      <c r="L60" s="57"/>
+      <c r="M60" s="57"/>
     </row>
     <row r="61" spans="2:13" ht="15.75" customHeight="1">
       <c r="B61" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C61" s="52"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C61" s="58"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="61"/>
       <c r="F61" s="15"/>
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
-      <c r="J61" s="95"/>
+      <c r="J61" s="22"/>
       <c r="K61" s="14"/>
-      <c r="L61" s="58"/>
-      <c r="M61" s="58"/>
+      <c r="L61" s="64"/>
+      <c r="M61" s="64"/>
     </row>
     <row r="62" spans="2:13" ht="15.75" customHeight="1">
       <c r="B62" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C62" s="53"/>
-      <c r="D62" s="56"/>
-      <c r="E62" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C62" s="59"/>
+      <c r="D62" s="62"/>
+      <c r="E62" s="63"/>
       <c r="F62" s="14"/>
       <c r="G62" s="16"/>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
-      <c r="J62" s="95"/>
+      <c r="J62" s="22"/>
       <c r="K62" s="14"/>
-      <c r="L62" s="59"/>
-      <c r="M62" s="59"/>
+      <c r="L62" s="65"/>
+      <c r="M62" s="65"/>
     </row>
     <row r="63" spans="2:13" ht="15.75" customHeight="1">
       <c r="B63" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C63" s="60"/>
-      <c r="D63" s="62"/>
-      <c r="E63" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C63" s="32"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="24"/>
       <c r="F63" s="12"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="66"/>
-      <c r="M63" s="66"/>
+      <c r="L63" s="27"/>
+      <c r="M63" s="27"/>
     </row>
     <row r="64" spans="2:13" ht="15.75" customHeight="1">
       <c r="B64" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" s="61"/>
-      <c r="D64" s="64"/>
-      <c r="E64" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C64" s="33"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="26"/>
       <c r="F64" s="4"/>
       <c r="G64" s="11"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="67"/>
-      <c r="M64" s="67"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="57"/>
     </row>
     <row r="65" spans="2:13" ht="15.75" customHeight="1">
       <c r="B65" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C65" s="52"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C65" s="58"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="61"/>
       <c r="F65" s="15"/>
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
-      <c r="J65" s="95"/>
+      <c r="J65" s="22"/>
       <c r="K65" s="14"/>
-      <c r="L65" s="58"/>
-      <c r="M65" s="58"/>
+      <c r="L65" s="64"/>
+      <c r="M65" s="64"/>
     </row>
     <row r="66" spans="2:13" ht="15.75" customHeight="1">
       <c r="B66" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C66" s="53"/>
-      <c r="D66" s="56"/>
-      <c r="E66" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C66" s="59"/>
+      <c r="D66" s="62"/>
+      <c r="E66" s="63"/>
       <c r="F66" s="14"/>
       <c r="G66" s="16"/>
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
-      <c r="J66" s="95"/>
+      <c r="J66" s="22"/>
       <c r="K66" s="14"/>
-      <c r="L66" s="59"/>
-      <c r="M66" s="59"/>
+      <c r="L66" s="65"/>
+      <c r="M66" s="65"/>
     </row>
     <row r="67" spans="2:13" ht="15.75" customHeight="1">
       <c r="B67" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C67" s="60"/>
-      <c r="D67" s="62"/>
-      <c r="E67" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C67" s="32"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="24"/>
       <c r="F67" s="12"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
-      <c r="L67" s="66"/>
-      <c r="M67" s="66"/>
+      <c r="L67" s="27"/>
+      <c r="M67" s="27"/>
     </row>
     <row r="68" spans="2:13" ht="15.75" customHeight="1">
       <c r="B68" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C68" s="61"/>
-      <c r="D68" s="64"/>
-      <c r="E68" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C68" s="33"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="26"/>
       <c r="F68" s="4"/>
       <c r="G68" s="11"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
-      <c r="L68" s="67"/>
-      <c r="M68" s="67"/>
+      <c r="L68" s="57"/>
+      <c r="M68" s="57"/>
     </row>
     <row r="69" spans="2:13" ht="15.75" customHeight="1">
       <c r="B69" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="52"/>
-      <c r="D69" s="54"/>
-      <c r="E69" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="C69" s="58"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="61"/>
       <c r="F69" s="15"/>
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
-      <c r="J69" s="95"/>
+      <c r="J69" s="22"/>
       <c r="K69" s="14"/>
-      <c r="L69" s="58"/>
-      <c r="M69" s="58"/>
+      <c r="L69" s="64"/>
+      <c r="M69" s="64"/>
     </row>
     <row r="70" spans="2:13" ht="15.75" customHeight="1">
       <c r="B70" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" s="53"/>
-      <c r="D70" s="56"/>
-      <c r="E70" s="57"/>
+        <v>20</v>
+      </c>
+      <c r="C70" s="59"/>
+      <c r="D70" s="62"/>
+      <c r="E70" s="63"/>
       <c r="F70" s="14"/>
       <c r="G70" s="16"/>
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
-      <c r="J70" s="95"/>
+      <c r="J70" s="22"/>
       <c r="K70" s="14"/>
-      <c r="L70" s="59"/>
-      <c r="M70" s="59"/>
+      <c r="L70" s="65"/>
+      <c r="M70" s="65"/>
     </row>
     <row r="71" spans="2:13" ht="15.75" customHeight="1">
       <c r="B71" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="60"/>
-      <c r="D71" s="62"/>
-      <c r="E71" s="63"/>
+        <v>19</v>
+      </c>
+      <c r="C71" s="32"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="24"/>
       <c r="F71" s="12"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
-      <c r="L71" s="66"/>
-      <c r="M71" s="66"/>
+      <c r="L71" s="27"/>
+      <c r="M71" s="27"/>
     </row>
     <row r="72" spans="2:13" ht="15.75" customHeight="1">
       <c r="B72" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C72" s="61"/>
-      <c r="D72" s="64"/>
-      <c r="E72" s="65"/>
+        <v>20</v>
+      </c>
+      <c r="C72" s="33"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="26"/>
       <c r="F72" s="4"/>
       <c r="G72" s="11"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
-      <c r="L72" s="67"/>
-      <c r="M72" s="67"/>
+      <c r="L72" s="57"/>
+      <c r="M72" s="57"/>
     </row>
     <row r="73" spans="2:13" ht="15.75" customHeight="1"/>
     <row r="74" spans="2:13" ht="15.75" customHeight="1"/>
@@ -4464,6 +3844,123 @@
     <filterColumn colId="10" showButton="0"/>
   </autoFilter>
   <mergeCells count="135">
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:E70"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:E72"/>
+    <mergeCell ref="L71:M71"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:E66"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:E68"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:E62"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:E64"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:E58"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:E60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:E54"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:E56"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:E50"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:E52"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:E46"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:E42"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:E44"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:E38"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:E40"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:E34"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:E36"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:E30"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:E26"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:E28"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:E18"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:E22"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:E24"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:E20"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
     <mergeCell ref="D15:E16"/>
     <mergeCell ref="L15:M15"/>
     <mergeCell ref="L16:M16"/>
@@ -4482,132 +3979,7 @@
     <mergeCell ref="D11:E12"/>
     <mergeCell ref="L11:M11"/>
     <mergeCell ref="L12:M12"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:E22"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:E24"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:E20"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:E18"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:E30"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:E32"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:E26"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:E28"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:E38"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:E40"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:E34"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:E36"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:E46"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:E42"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:E44"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:E54"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:E56"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:E50"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:E52"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:E62"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:E64"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:E58"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:E60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:E70"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:E72"/>
-    <mergeCell ref="L71:M71"/>
-    <mergeCell ref="L72:M72"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:E66"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:E68"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="L68:M68"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11:H72" xr:uid="{5C903669-5CA5-4145-8091-8AE9E7D9FFEE}">
-      <formula1>"Cargador 966H1, Cargador 966H2, Cargador DL320A, Excavadora PC200-8, Excavadora PC210-10, Camioneta GTK801, Camioneta JXV805, Otros"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I11:I72" xr:uid="{0B6DC62B-9A6E-451F-AD8A-FAC8E479D6F4}">
-      <formula1>"Trasiego MMPP, Trasiego de escoria, Descargue de volcos,Actividad adicional, Otros"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup scale="46" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/EquiposUnidos/app/src/main/res/raw/template_user.xlsx
+++ b/EquiposUnidos/app/src/main/res/raw/template_user.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elksi\Android\williApp\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813BAB3C-383C-4536-815E-E56465BFF8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E581E1-A957-418D-9FFD-FAA423AF5CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="897" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12504" tabRatio="897" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eider Melendez" sheetId="10" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="21">
   <si>
     <t>NOVEDADES DE NOMINA</t>
   </si>
@@ -122,7 +122,7 @@
     <numFmt numFmtId="165" formatCode="hh:mm:ss;@"/>
     <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,6 +630,32 @@
     <xf numFmtId="49" fontId="10" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -643,6 +669,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -652,12 +679,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -712,27 +733,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1641,7 +1641,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:AD999"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" customWidth="1"/>
@@ -1656,19 +1656,19 @@
     <col min="14" max="30" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="14.4">
-      <c r="B2" s="34"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="43" t="s">
+    <row r="2" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
       <c r="L2" s="18" t="s">
         <v>3</v>
       </c>
@@ -1676,17 +1676,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="14.4">
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
+    <row r="3" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
       <c r="L3" s="19" t="s">
         <v>4</v>
       </c>
@@ -1694,17 +1694,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="14.4">
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
+    <row r="4" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="20" t="s">
         <v>5</v>
       </c>
@@ -1712,88 +1712,88 @@
         <v>45211</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="14.4">
-      <c r="B6" s="50" t="s">
+    <row r="6" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B6" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="51" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="2:14" ht="14.4">
-      <c r="B7" s="50" t="s">
+    <row r="7" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="53">
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="62">
         <v>1128048038</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="54"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="63"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="2:14" ht="14.4">
-      <c r="B8" s="50" t="s">
+    <row r="8" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B8" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="53" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="54"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="63"/>
       <c r="N8" s="21"/>
     </row>
-    <row r="9" spans="2:14" ht="14.4">
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-    </row>
-    <row r="10" spans="2:14" ht="14.4">
+    <row r="9" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+    </row>
+    <row r="10" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="29"/>
+      <c r="E10" s="40"/>
       <c r="F10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1812,266 +1812,266 @@
       <c r="K10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="30" t="s">
+      <c r="L10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="31"/>
-    </row>
-    <row r="11" spans="2:14" ht="14.4">
+      <c r="M10" s="42"/>
+    </row>
+    <row r="11" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="12"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-    </row>
-    <row r="12" spans="2:14" ht="14.4">
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+    </row>
+    <row r="12" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="36"/>
       <c r="F12" s="4"/>
       <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-    </row>
-    <row r="13" spans="2:14" ht="14.4">
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+    </row>
+    <row r="13" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="61"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="22"/>
       <c r="K13" s="14"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-    </row>
-    <row r="14" spans="2:14" ht="14.4">
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+    </row>
+    <row r="14" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="63"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="22"/>
       <c r="K14" s="14"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="64"/>
-    </row>
-    <row r="15" spans="2:14" ht="14.4">
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+    </row>
+    <row r="15" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
       <c r="F15" s="12"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-    </row>
-    <row r="16" spans="2:14" ht="14.4">
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+    </row>
+    <row r="16" spans="2:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="26"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="36"/>
       <c r="F16" s="4"/>
       <c r="G16" s="11"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-    </row>
-    <row r="17" spans="2:30" ht="14.4">
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+    </row>
+    <row r="17" spans="2:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="61"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="15"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="22"/>
       <c r="K17" s="14"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
-    </row>
-    <row r="18" spans="2:30" ht="14.4">
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+    </row>
+    <row r="18" spans="2:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28"/>
       <c r="F18" s="14"/>
       <c r="G18" s="16"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="22"/>
       <c r="K18" s="14"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-    </row>
-    <row r="19" spans="2:30" ht="14.4">
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+    </row>
+    <row r="19" spans="2:30" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="12"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-    </row>
-    <row r="20" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+    </row>
+    <row r="20" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="26"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="4"/>
       <c r="G20" s="11"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-    </row>
-    <row r="21" spans="2:30" ht="15" customHeight="1">
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+    </row>
+    <row r="21" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="61"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="15"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
       <c r="J21" s="22"/>
       <c r="K21" s="14"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-    </row>
-    <row r="22" spans="2:30" ht="15" customHeight="1">
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+    </row>
+    <row r="22" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="28"/>
       <c r="F22" s="14"/>
       <c r="G22" s="16"/>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="22"/>
       <c r="K22" s="14"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-    </row>
-    <row r="23" spans="2:30" ht="15" customHeight="1">
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+    </row>
+    <row r="23" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="34"/>
       <c r="F23" s="12"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-    </row>
-    <row r="24" spans="2:30" ht="15" customHeight="1">
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+    </row>
+    <row r="24" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="26"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="36"/>
       <c r="F24" s="4"/>
       <c r="G24" s="11"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-    </row>
-    <row r="25" spans="2:30" ht="15" customHeight="1">
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+    </row>
+    <row r="25" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="58"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="61"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="15"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="22"/>
       <c r="K25" s="14"/>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
-    </row>
-    <row r="26" spans="2:30" ht="15" customHeight="1">
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+    </row>
+    <row r="26" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="59"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="63"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="28"/>
       <c r="F26" s="14"/>
       <c r="G26" s="16"/>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="22"/>
       <c r="K26" s="14"/>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -2090,21 +2090,21 @@
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
     </row>
-    <row r="27" spans="2:30" ht="15" customHeight="1">
+    <row r="27" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -2123,37 +2123,37 @@
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
     </row>
-    <row r="28" spans="2:30" ht="15" customHeight="1">
+    <row r="28" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="36"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-    </row>
-    <row r="29" spans="2:30" ht="15" customHeight="1">
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+    </row>
+    <row r="29" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="61"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="15"/>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
       <c r="J29" s="22"/>
       <c r="K29" s="14"/>
-      <c r="L29" s="64"/>
-      <c r="M29" s="64"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -2172,69 +2172,69 @@
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
     </row>
-    <row r="30" spans="2:30" ht="15" customHeight="1">
+    <row r="30" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="59"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="63"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="28"/>
       <c r="F30" s="14"/>
       <c r="G30" s="16"/>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="22"/>
       <c r="K30" s="14"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-    </row>
-    <row r="31" spans="2:30" ht="15" customHeight="1">
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+    </row>
+    <row r="31" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="24"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="34"/>
       <c r="F31" s="12"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-    </row>
-    <row r="32" spans="2:30" ht="15" customHeight="1">
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
+    </row>
+    <row r="32" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="4"/>
       <c r="G32" s="11"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-    </row>
-    <row r="33" spans="2:30" ht="15" customHeight="1">
+      <c r="L32" s="37"/>
+      <c r="M32" s="37"/>
+    </row>
+    <row r="33" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="58"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="61"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="15"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="22"/>
       <c r="K33" s="14"/>
-      <c r="L33" s="65"/>
-      <c r="M33" s="65"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -2253,53 +2253,53 @@
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
     </row>
-    <row r="34" spans="2:30" ht="15.75" customHeight="1">
+    <row r="34" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="59"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="63"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="28"/>
       <c r="F34" s="14"/>
       <c r="G34" s="16"/>
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
       <c r="J34" s="22"/>
       <c r="K34" s="14"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-    </row>
-    <row r="35" spans="2:30" ht="15" customHeight="1">
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+    </row>
+    <row r="35" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="24"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="34"/>
       <c r="F35" s="12"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-    </row>
-    <row r="36" spans="2:30" ht="15" customHeight="1">
+      <c r="L35" s="37"/>
+      <c r="M35" s="37"/>
+    </row>
+    <row r="36" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="33"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="26"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="36"/>
       <c r="F36" s="4"/>
       <c r="G36" s="11"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
+      <c r="L36" s="37"/>
+      <c r="M36" s="37"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
@@ -2318,69 +2318,69 @@
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
     </row>
-    <row r="37" spans="2:30" ht="15" customHeight="1">
+    <row r="37" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="58"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="61"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="26"/>
       <c r="F37" s="15"/>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
       <c r="J37" s="22"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
-    </row>
-    <row r="38" spans="2:30" ht="15" customHeight="1">
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+    </row>
+    <row r="38" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="63"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="28"/>
       <c r="F38" s="14"/>
       <c r="G38" s="16"/>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
       <c r="J38" s="22"/>
       <c r="K38" s="14"/>
-      <c r="L38" s="64"/>
-      <c r="M38" s="64"/>
-    </row>
-    <row r="39" spans="2:30" ht="15" customHeight="1">
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+    </row>
+    <row r="39" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="32"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="24"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="34"/>
       <c r="F39" s="12"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-    </row>
-    <row r="40" spans="2:30" ht="15" customHeight="1">
+      <c r="L39" s="37"/>
+      <c r="M39" s="37"/>
+    </row>
+    <row r="40" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="26"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="36"/>
       <c r="F40" s="4"/>
       <c r="G40" s="11"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -2399,1451 +2399,2182 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
     </row>
-    <row r="41" spans="2:30" ht="15.75" customHeight="1">
+    <row r="41" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="58"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="26"/>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
       <c r="J41" s="22"/>
       <c r="K41" s="14"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="64"/>
-    </row>
-    <row r="42" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+    </row>
+    <row r="42" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="59"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="63"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="28"/>
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="22"/>
       <c r="K42" s="14"/>
-      <c r="L42" s="65"/>
-      <c r="M42" s="65"/>
-    </row>
-    <row r="43" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+    </row>
+    <row r="43" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="24"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
       <c r="F43" s="12"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-    </row>
-    <row r="44" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L43" s="37"/>
+      <c r="M43" s="37"/>
+    </row>
+    <row r="44" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="26"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="36"/>
       <c r="F44" s="4"/>
       <c r="G44" s="11"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="57"/>
-    </row>
-    <row r="45" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+    </row>
+    <row r="45" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="58"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="61"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="26"/>
       <c r="F45" s="15"/>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="22"/>
       <c r="K45" s="14"/>
-      <c r="L45" s="64"/>
-      <c r="M45" s="64"/>
-    </row>
-    <row r="46" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+    </row>
+    <row r="46" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="59"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="63"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="28"/>
       <c r="F46" s="14"/>
       <c r="G46" s="16"/>
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
       <c r="J46" s="22"/>
       <c r="K46" s="14"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="65"/>
-    </row>
-    <row r="47" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+    </row>
+    <row r="47" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="24"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="34"/>
       <c r="F47" s="12"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-    </row>
-    <row r="48" spans="2:30" ht="15.75" customHeight="1">
+      <c r="L47" s="37"/>
+      <c r="M47" s="37"/>
+    </row>
+    <row r="48" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="33"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="26"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="36"/>
       <c r="F48" s="4"/>
       <c r="G48" s="11"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="57"/>
-    </row>
-    <row r="49" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L48" s="38"/>
+      <c r="M48" s="38"/>
+    </row>
+    <row r="49" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="58"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="61"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="26"/>
       <c r="F49" s="15"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="22"/>
       <c r="K49" s="14"/>
-      <c r="L49" s="64"/>
-      <c r="M49" s="64"/>
-    </row>
-    <row r="50" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+    </row>
+    <row r="50" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="59"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="63"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="28"/>
       <c r="F50" s="14"/>
       <c r="G50" s="16"/>
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
       <c r="J50" s="22"/>
       <c r="K50" s="14"/>
-      <c r="L50" s="65"/>
-      <c r="M50" s="65"/>
-    </row>
-    <row r="51" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+    </row>
+    <row r="51" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="24"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="34"/>
       <c r="F51" s="12"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
-    </row>
-    <row r="52" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L51" s="37"/>
+      <c r="M51" s="37"/>
+    </row>
+    <row r="52" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="33"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="26"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="36"/>
       <c r="F52" s="4"/>
       <c r="G52" s="11"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
-      <c r="L52" s="57"/>
-      <c r="M52" s="57"/>
-    </row>
-    <row r="53" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L52" s="38"/>
+      <c r="M52" s="38"/>
+    </row>
+    <row r="53" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C53" s="58"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="61"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="26"/>
       <c r="F53" s="15"/>
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="22"/>
       <c r="K53" s="14"/>
-      <c r="L53" s="64"/>
-      <c r="M53" s="64"/>
-    </row>
-    <row r="54" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L53" s="29"/>
+      <c r="M53" s="29"/>
+    </row>
+    <row r="54" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="59"/>
-      <c r="D54" s="62"/>
-      <c r="E54" s="63"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="28"/>
       <c r="F54" s="14"/>
       <c r="G54" s="16"/>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="22"/>
       <c r="K54" s="14"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
-    </row>
-    <row r="55" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+    </row>
+    <row r="55" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="24"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="34"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-    </row>
-    <row r="56" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L55" s="37"/>
+      <c r="M55" s="37"/>
+    </row>
+    <row r="56" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C56" s="33"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="26"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
-      <c r="L56" s="57"/>
-      <c r="M56" s="57"/>
-    </row>
-    <row r="57" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L56" s="38"/>
+      <c r="M56" s="38"/>
+    </row>
+    <row r="57" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="58"/>
-      <c r="D57" s="60"/>
-      <c r="E57" s="61"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="26"/>
       <c r="F57" s="15"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="22"/>
       <c r="K57" s="14"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="64"/>
-    </row>
-    <row r="58" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+    </row>
+    <row r="58" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="59"/>
-      <c r="D58" s="62"/>
-      <c r="E58" s="63"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="28"/>
       <c r="F58" s="14"/>
       <c r="G58" s="16"/>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="22"/>
       <c r="K58" s="14"/>
-      <c r="L58" s="65"/>
-      <c r="M58" s="65"/>
-    </row>
-    <row r="59" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+    </row>
+    <row r="59" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="24"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="34"/>
       <c r="F59" s="12"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-    </row>
-    <row r="60" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L59" s="37"/>
+      <c r="M59" s="37"/>
+    </row>
+    <row r="60" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="26"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="36"/>
       <c r="F60" s="4"/>
       <c r="G60" s="11"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
-      <c r="L60" s="57"/>
-      <c r="M60" s="57"/>
-    </row>
-    <row r="61" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L60" s="38"/>
+      <c r="M60" s="38"/>
+    </row>
+    <row r="61" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="58"/>
-      <c r="D61" s="60"/>
-      <c r="E61" s="61"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="26"/>
       <c r="F61" s="15"/>
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
       <c r="J61" s="22"/>
       <c r="K61" s="14"/>
-      <c r="L61" s="64"/>
-      <c r="M61" s="64"/>
-    </row>
-    <row r="62" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+    </row>
+    <row r="62" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C62" s="59"/>
-      <c r="D62" s="62"/>
-      <c r="E62" s="63"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="28"/>
       <c r="F62" s="14"/>
       <c r="G62" s="16"/>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="22"/>
       <c r="K62" s="14"/>
-      <c r="L62" s="65"/>
-      <c r="M62" s="65"/>
-    </row>
-    <row r="63" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
+    </row>
+    <row r="63" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="24"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="34"/>
       <c r="F63" s="12"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-    </row>
-    <row r="64" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L63" s="37"/>
+      <c r="M63" s="37"/>
+    </row>
+    <row r="64" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C64" s="33"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="26"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="36"/>
       <c r="F64" s="4"/>
       <c r="G64" s="11"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
-      <c r="L64" s="57"/>
-      <c r="M64" s="57"/>
-    </row>
-    <row r="65" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L64" s="38"/>
+      <c r="M64" s="38"/>
+    </row>
+    <row r="65" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="58"/>
-      <c r="D65" s="60"/>
-      <c r="E65" s="61"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="26"/>
       <c r="F65" s="15"/>
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
       <c r="J65" s="22"/>
       <c r="K65" s="14"/>
-      <c r="L65" s="64"/>
-      <c r="M65" s="64"/>
-    </row>
-    <row r="66" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L65" s="29"/>
+      <c r="M65" s="29"/>
+    </row>
+    <row r="66" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C66" s="59"/>
-      <c r="D66" s="62"/>
-      <c r="E66" s="63"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="28"/>
       <c r="F66" s="14"/>
       <c r="G66" s="16"/>
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="22"/>
       <c r="K66" s="14"/>
-      <c r="L66" s="65"/>
-      <c r="M66" s="65"/>
-    </row>
-    <row r="67" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L66" s="30"/>
+      <c r="M66" s="30"/>
+    </row>
+    <row r="67" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="32"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="24"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="34"/>
       <c r="F67" s="12"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-    </row>
-    <row r="68" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L67" s="37"/>
+      <c r="M67" s="37"/>
+    </row>
+    <row r="68" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C68" s="33"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="26"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="36"/>
       <c r="F68" s="4"/>
       <c r="G68" s="11"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
-      <c r="L68" s="57"/>
-      <c r="M68" s="57"/>
-    </row>
-    <row r="69" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L68" s="38"/>
+      <c r="M68" s="38"/>
+    </row>
+    <row r="69" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="58"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="61"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="26"/>
       <c r="F69" s="15"/>
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
       <c r="J69" s="22"/>
       <c r="K69" s="14"/>
-      <c r="L69" s="64"/>
-      <c r="M69" s="64"/>
-    </row>
-    <row r="70" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+    </row>
+    <row r="70" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="59"/>
-      <c r="D70" s="62"/>
-      <c r="E70" s="63"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="28"/>
       <c r="F70" s="14"/>
       <c r="G70" s="16"/>
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
       <c r="J70" s="22"/>
       <c r="K70" s="14"/>
-      <c r="L70" s="65"/>
-      <c r="M70" s="65"/>
-    </row>
-    <row r="71" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+    </row>
+    <row r="71" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C71" s="32"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="24"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="34"/>
       <c r="F71" s="12"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
-      <c r="L71" s="27"/>
-      <c r="M71" s="27"/>
-    </row>
-    <row r="72" spans="2:13" ht="15.75" customHeight="1">
+      <c r="L71" s="37"/>
+      <c r="M71" s="37"/>
+    </row>
+    <row r="72" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C72" s="33"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="26"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="36"/>
       <c r="F72" s="4"/>
       <c r="G72" s="11"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
-      <c r="L72" s="57"/>
-      <c r="M72" s="57"/>
-    </row>
-    <row r="73" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="74" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="75" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="76" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="77" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="78" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="79" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="80" spans="2:13" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
+      <c r="L72" s="38"/>
+      <c r="M72" s="38"/>
+    </row>
+    <row r="73" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="23"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="29"/>
+      <c r="M73" s="29"/>
+    </row>
+    <row r="74" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="24"/>
+      <c r="D74" s="27"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="30"/>
+      <c r="M74" s="30"/>
+    </row>
+    <row r="75" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="31"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="37"/>
+      <c r="M75" s="37"/>
+    </row>
+    <row r="76" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="32"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="38"/>
+      <c r="M76" s="38"/>
+    </row>
+    <row r="77" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="23"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="14"/>
+      <c r="L77" s="29"/>
+      <c r="M77" s="29"/>
+    </row>
+    <row r="78" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="24"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="22"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="30"/>
+      <c r="M78" s="30"/>
+    </row>
+    <row r="79" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="31"/>
+      <c r="D79" s="33"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="37"/>
+      <c r="M79" s="37"/>
+    </row>
+    <row r="80" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="32"/>
+      <c r="D80" s="35"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="38"/>
+      <c r="M80" s="38"/>
+    </row>
+    <row r="81" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="23"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="22"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="29"/>
+      <c r="M81" s="29"/>
+    </row>
+    <row r="82" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="24"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="28"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="16"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="22"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="30"/>
+      <c r="M82" s="30"/>
+    </row>
+    <row r="83" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" s="31"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="34"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="37"/>
+      <c r="M83" s="37"/>
+    </row>
+    <row r="84" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="32"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="38"/>
+      <c r="M84" s="38"/>
+    </row>
+    <row r="85" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" s="23"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="22"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="29"/>
+      <c r="M85" s="29"/>
+    </row>
+    <row r="86" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" s="24"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="28"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="22"/>
+      <c r="K86" s="14"/>
+      <c r="L86" s="30"/>
+      <c r="M86" s="30"/>
+    </row>
+    <row r="87" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" s="31"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="34"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="37"/>
+      <c r="M87" s="37"/>
+    </row>
+    <row r="88" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="32"/>
+      <c r="D88" s="35"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="38"/>
+      <c r="M88" s="38"/>
+    </row>
+    <row r="89" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="23"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="15"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="22"/>
+      <c r="K89" s="14"/>
+      <c r="L89" s="29"/>
+      <c r="M89" s="29"/>
+    </row>
+    <row r="90" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" s="24"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="16"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="22"/>
+      <c r="K90" s="14"/>
+      <c r="L90" s="30"/>
+      <c r="M90" s="30"/>
+    </row>
+    <row r="91" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" s="31"/>
+      <c r="D91" s="33"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="37"/>
+      <c r="M91" s="37"/>
+    </row>
+    <row r="92" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="32"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="38"/>
+      <c r="M92" s="38"/>
+    </row>
+    <row r="93" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" s="23"/>
+      <c r="D93" s="25"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="15"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="22"/>
+      <c r="K93" s="14"/>
+      <c r="L93" s="29"/>
+      <c r="M93" s="29"/>
+    </row>
+    <row r="94" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B94" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" s="24"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="28"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="22"/>
+      <c r="K94" s="14"/>
+      <c r="L94" s="30"/>
+      <c r="M94" s="30"/>
+    </row>
+    <row r="95" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" s="31"/>
+      <c r="D95" s="33"/>
+      <c r="E95" s="34"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="37"/>
+      <c r="M95" s="37"/>
+    </row>
+    <row r="96" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="32"/>
+      <c r="D96" s="35"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="38"/>
+      <c r="M96" s="38"/>
+    </row>
+    <row r="97" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="23"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="22"/>
+      <c r="K97" s="14"/>
+      <c r="L97" s="29"/>
+      <c r="M97" s="29"/>
+    </row>
+    <row r="98" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="24"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="16"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="14"/>
+      <c r="J98" s="22"/>
+      <c r="K98" s="14"/>
+      <c r="L98" s="30"/>
+      <c r="M98" s="30"/>
+    </row>
+    <row r="99" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="31"/>
+      <c r="D99" s="33"/>
+      <c r="E99" s="34"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="37"/>
+      <c r="M99" s="37"/>
+    </row>
+    <row r="100" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="32"/>
+      <c r="D100" s="35"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="38"/>
+      <c r="M100" s="38"/>
+    </row>
+    <row r="101" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="23"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="26"/>
+      <c r="F101" s="15"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="22"/>
+      <c r="K101" s="14"/>
+      <c r="L101" s="29"/>
+      <c r="M101" s="29"/>
+    </row>
+    <row r="102" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" s="24"/>
+      <c r="D102" s="27"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="22"/>
+      <c r="K102" s="14"/>
+      <c r="L102" s="30"/>
+      <c r="M102" s="30"/>
+    </row>
+    <row r="103" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" s="31"/>
+      <c r="D103" s="33"/>
+      <c r="E103" s="34"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="37"/>
+      <c r="M103" s="37"/>
+    </row>
+    <row r="104" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="32"/>
+      <c r="D104" s="35"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="11"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="38"/>
+      <c r="M104" s="38"/>
+    </row>
+    <row r="105" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C105" s="23"/>
+      <c r="D105" s="25"/>
+      <c r="E105" s="26"/>
+      <c r="F105" s="15"/>
+      <c r="G105" s="14"/>
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="22"/>
+      <c r="K105" s="14"/>
+      <c r="L105" s="29"/>
+      <c r="M105" s="29"/>
+    </row>
+    <row r="106" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B106" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" s="24"/>
+      <c r="D106" s="27"/>
+      <c r="E106" s="28"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="16"/>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14"/>
+      <c r="J106" s="22"/>
+      <c r="K106" s="14"/>
+      <c r="L106" s="30"/>
+      <c r="M106" s="30"/>
+    </row>
+    <row r="107" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B107" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C107" s="31"/>
+      <c r="D107" s="33"/>
+      <c r="E107" s="34"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="37"/>
+      <c r="M107" s="37"/>
+    </row>
+    <row r="108" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="32"/>
+      <c r="D108" s="35"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="38"/>
+      <c r="M108" s="38"/>
+    </row>
+    <row r="109" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="B10:M68" xr:uid="{04431152-7F1A-4FED-9882-0258CB9CD38F}">
     <filterColumn colId="2" showButton="0"/>
     <filterColumn colId="10" showButton="0"/>
   </autoFilter>
-  <mergeCells count="135">
+  <mergeCells count="207">
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="D103:E104"/>
+    <mergeCell ref="L103:M103"/>
+    <mergeCell ref="L104:M104"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="D105:E106"/>
+    <mergeCell ref="L105:M105"/>
+    <mergeCell ref="L106:M106"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:E108"/>
+    <mergeCell ref="L107:M107"/>
+    <mergeCell ref="L108:M108"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:E98"/>
+    <mergeCell ref="L97:M97"/>
+    <mergeCell ref="L98:M98"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="D99:E100"/>
+    <mergeCell ref="L99:M99"/>
+    <mergeCell ref="L100:M100"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="D101:E102"/>
+    <mergeCell ref="L101:M101"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:E92"/>
+    <mergeCell ref="L91:M91"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="D93:E94"/>
+    <mergeCell ref="L93:M93"/>
+    <mergeCell ref="L94:M94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:E96"/>
+    <mergeCell ref="L95:M95"/>
+    <mergeCell ref="L96:M96"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:E86"/>
+    <mergeCell ref="L85:M85"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:E88"/>
+    <mergeCell ref="L87:M87"/>
+    <mergeCell ref="L88:M88"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:E90"/>
+    <mergeCell ref="L89:M89"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:E80"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:E82"/>
+    <mergeCell ref="L81:M81"/>
+    <mergeCell ref="L82:M82"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:E84"/>
+    <mergeCell ref="L83:M83"/>
+    <mergeCell ref="L84:M84"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:E74"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:E76"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:E78"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B2:D4"/>
+    <mergeCell ref="E2:K4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:M6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:E22"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:E24"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:E20"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:E18"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:E30"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:E26"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:E28"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:E38"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:E40"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:E34"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:E36"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:E46"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E48"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:E42"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:E44"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:E54"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:E56"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:E50"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:E52"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:E62"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:E64"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:E58"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:E60"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="L60:M60"/>
     <mergeCell ref="C69:C70"/>
     <mergeCell ref="D69:E70"/>
     <mergeCell ref="L69:M69"/>
@@ -3860,125 +4591,6 @@
     <mergeCell ref="D67:E68"/>
     <mergeCell ref="L67:M67"/>
     <mergeCell ref="L68:M68"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:E62"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:E64"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:E58"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:E60"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:E54"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:E56"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:E50"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:E52"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:E46"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:E42"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:E44"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:E38"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:E40"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:E34"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:E36"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:E30"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:E32"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:E26"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:E28"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:E18"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:E22"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:E24"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:E20"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B2:D4"/>
-    <mergeCell ref="E2:K4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:M6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:M7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup scale="46" orientation="landscape" r:id="rId1"/>
